--- a/SRPT.xlsx
+++ b/SRPT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52EB995-E08B-46DE-BC9C-BC1C7098F23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A88648B-57AD-417C-98E6-BE8BB7213BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41830" yWindow="9950" windowWidth="34230" windowHeight="15680" activeTab="1" xr2:uid="{79CAE26F-8736-4C5E-9FC6-A2D7A01B0567}"/>
+    <workbookView xWindow="6490" yWindow="8380" windowWidth="27450" windowHeight="11540" activeTab="1" xr2:uid="{79CAE26F-8736-4C5E-9FC6-A2D7A01B0567}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 11/3/25 consensus: 351m</t>
       </text>
     </comment>
-    <comment ref="AQ13" authorId="5" shapeId="0" xr:uid="{79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}">
+    <comment ref="AU13" authorId="5" shapeId="0" xr:uid="{79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -103,7 +103,7 @@
 Consensus 3.0B</t>
       </text>
     </comment>
-    <comment ref="AR13" authorId="6" shapeId="0" xr:uid="{4BF41E21-6626-4EBB-BC28-DD3A3AEE92C2}">
+    <comment ref="AV13" authorId="6" shapeId="0" xr:uid="{4BF41E21-6626-4EBB-BC28-DD3A3AEE92C2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="258">
   <si>
     <t>Price</t>
   </si>
@@ -878,6 +878,18 @@
   </si>
   <si>
     <t>Buyback</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -1129,16 +1141,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>69082</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>25121</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>81781</xdr:rowOff>
+      <xdr:rowOff>8512</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>69082</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>25121</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>112346</xdr:rowOff>
+      <xdr:rowOff>39077</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1153,8 +1165,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15563082" y="81781"/>
-          <a:ext cx="0" cy="13092027"/>
+          <a:off x="16740275" y="8512"/>
+          <a:ext cx="0" cy="13253219"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1179,13 +1191,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>42</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>26737</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>50132</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>26737</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>122115</xdr:rowOff>
@@ -1775,11 +1787,11 @@
     <text>5/6/25 consensus 828m
 11/3/25 consensus: 351m</text>
   </threadedComment>
-  <threadedComment ref="AQ13" dT="2025-05-06T15:53:17.18" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}">
+  <threadedComment ref="AU13" dT="2025-05-06T15:53:17.18" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{79BDC40B-94ED-4D00-94B2-1CB4305DAAA9}">
     <text>Q424 product guidance: 2.9-3.1B
 Consensus 3.0B</text>
   </threadedComment>
-  <threadedComment ref="AR13" dT="2025-05-06T15:46:11.33" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{4BF41E21-6626-4EBB-BC28-DD3A3AEE92C2}">
+  <threadedComment ref="AV13" dT="2025-05-06T15:46:11.33" personId="{0ED4F94C-7603-49B0-A19F-451A0F5F06CB}" id="{4BF41E21-6626-4EBB-BC28-DD3A3AEE92C2}">
     <text>5/6/25 consensus 3.76B</text>
   </threadedComment>
 </ThreadedComments>
@@ -2209,23 +2221,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3CE2201-9B97-4447-A1A2-DF8707285205}">
-  <dimension ref="A1:BD75"/>
+  <dimension ref="A1:BH75"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="17" width="9.1796875" style="3"/>
-    <col min="42" max="42" width="9.453125" customWidth="1"/>
-    <col min="43" max="43" width="8.81640625" customWidth="1"/>
-    <col min="56" max="56" width="12" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.453125" customWidth="1"/>
+    <col min="47" max="47" width="8.81640625" customWidth="1"/>
+    <col min="60" max="60" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
@@ -2298,111 +2310,123 @@
       <c r="Z2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AB2">
+      <c r="AA2" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="AF2">
         <v>2010</v>
       </c>
-      <c r="AC2">
-        <f>+AB2+1</f>
+      <c r="AG2">
+        <f>+AF2+1</f>
         <v>2011</v>
       </c>
-      <c r="AD2">
-        <f t="shared" ref="AD2:AS2" si="0">+AC2+1</f>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AW2" si="0">+AG2+1</f>
         <v>2012</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <f t="shared" si="0"/>
         <v>2013</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <f t="shared" si="0"/>
         <v>2014</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <f t="shared" si="0"/>
         <v>2015</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <f t="shared" si="0"/>
         <v>2016</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <f t="shared" si="0"/>
         <v>2017</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <f t="shared" si="0"/>
         <v>2020</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <f t="shared" si="0"/>
         <v>2021</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="AT2">
-        <f t="shared" ref="AT2" si="1">+AS2+1</f>
+      <c r="AX2">
+        <f t="shared" ref="AX2" si="1">+AW2+1</f>
         <v>2028</v>
       </c>
-      <c r="AU2">
-        <f t="shared" ref="AU2" si="2">+AT2+1</f>
+      <c r="AY2">
+        <f t="shared" ref="AY2" si="2">+AX2+1</f>
         <v>2029</v>
       </c>
-      <c r="AV2">
-        <f t="shared" ref="AV2" si="3">+AU2+1</f>
+      <c r="AZ2">
+        <f t="shared" ref="AZ2" si="3">+AY2+1</f>
         <v>2030</v>
       </c>
-      <c r="AW2">
-        <f t="shared" ref="AW2" si="4">+AV2+1</f>
+      <c r="BA2">
+        <f t="shared" ref="BA2" si="4">+AZ2+1</f>
         <v>2031</v>
       </c>
-      <c r="AX2">
-        <f t="shared" ref="AX2" si="5">+AW2+1</f>
+      <c r="BB2">
+        <f t="shared" ref="BB2" si="5">+BA2+1</f>
         <v>2032</v>
       </c>
-      <c r="AY2">
-        <f t="shared" ref="AY2" si="6">+AX2+1</f>
+      <c r="BC2">
+        <f t="shared" ref="BC2" si="6">+BB2+1</f>
         <v>2033</v>
       </c>
-      <c r="AZ2">
-        <f t="shared" ref="AZ2" si="7">+AY2+1</f>
+      <c r="BD2">
+        <f t="shared" ref="BD2" si="7">+BC2+1</f>
         <v>2034</v>
       </c>
-      <c r="BA2">
-        <f t="shared" ref="BA2" si="8">+AZ2+1</f>
+      <c r="BE2">
+        <f t="shared" ref="BE2" si="8">+BD2+1</f>
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>93</v>
       </c>
@@ -2425,27 +2449,19 @@
       </c>
       <c r="Z3" s="5">
         <f t="shared" si="9"/>
-        <v>31.25</v>
-      </c>
-      <c r="AP3" s="2">
-        <f>+AP6/3.2</f>
+        <v>34.5</v>
+      </c>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AT3" s="2">
+        <f>+AT6/3.2</f>
         <v>256.51781249999999</v>
       </c>
-      <c r="AQ3" s="2">
-        <f>+AQ6/3.2</f>
-        <v>277.60968750000001</v>
-      </c>
-      <c r="AR3">
-        <v>800</v>
-      </c>
-      <c r="AS3">
-        <v>800</v>
-      </c>
-      <c r="AT3">
-        <v>800</v>
-      </c>
-      <c r="AU3">
-        <v>800</v>
+      <c r="AU3" s="2">
+        <f>+AU6/3.2</f>
+        <v>280.85968749999995</v>
       </c>
       <c r="AV3">
         <v>800</v>
@@ -2465,8 +2481,20 @@
       <c r="BA3">
         <v>800</v>
       </c>
-    </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="BB3">
+        <v>800</v>
+      </c>
+      <c r="BC3">
+        <v>800</v>
+      </c>
+      <c r="BD3">
+        <v>800</v>
+      </c>
+      <c r="BE3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>92</v>
       </c>
@@ -2491,57 +2519,61 @@
       </c>
       <c r="Z4" s="2">
         <f t="shared" si="10"/>
-        <v>877.60968749999995</v>
-      </c>
-      <c r="AP4" s="2">
+        <v>880.85968749999995</v>
+      </c>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AT4" s="2">
         <v>600</v>
       </c>
-      <c r="AQ4" s="2">
-        <f>+AP4+AQ3</f>
-        <v>877.60968750000006</v>
-      </c>
-      <c r="AR4" s="2">
-        <f>+AQ4+AR3</f>
-        <v>1677.6096875000001</v>
-      </c>
-      <c r="AS4" s="2">
-        <f t="shared" ref="AS4:AX4" si="11">+AR4+AS3</f>
-        <v>2477.6096875000003</v>
-      </c>
-      <c r="AT4" s="2">
-        <f t="shared" si="11"/>
-        <v>3277.6096875000003</v>
-      </c>
       <c r="AU4" s="2">
-        <f t="shared" si="11"/>
-        <v>4077.6096875000003</v>
+        <f>+AT4+AU3</f>
+        <v>880.85968749999995</v>
       </c>
       <c r="AV4" s="2">
-        <f t="shared" si="11"/>
-        <v>4877.6096875000003</v>
+        <f>+AU4+AV3</f>
+        <v>1680.8596874999998</v>
       </c>
       <c r="AW4" s="2">
-        <f t="shared" si="11"/>
-        <v>5677.6096875000003</v>
+        <f t="shared" ref="AW4:BB4" si="11">+AV4+AW3</f>
+        <v>2480.8596874999998</v>
       </c>
       <c r="AX4" s="2">
         <f t="shared" si="11"/>
-        <v>6477.6096875000003</v>
+        <v>3280.8596874999998</v>
       </c>
       <c r="AY4" s="2">
-        <f t="shared" ref="AY4" si="12">+AX4+AY3</f>
-        <v>7277.6096875000003</v>
+        <f t="shared" si="11"/>
+        <v>4080.8596874999998</v>
       </c>
       <c r="AZ4" s="2">
-        <f t="shared" ref="AZ4" si="13">+AY4+AZ3</f>
-        <v>8077.6096875000003</v>
+        <f t="shared" si="11"/>
+        <v>4880.8596875000003</v>
       </c>
       <c r="BA4" s="2">
-        <f t="shared" ref="BA4" si="14">+AZ4+BA3</f>
-        <v>8877.6096875000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v>5680.8596875000003</v>
+      </c>
+      <c r="BB4" s="2">
+        <f t="shared" si="11"/>
+        <v>6480.8596875000003</v>
+      </c>
+      <c r="BC4" s="2">
+        <f t="shared" ref="BC4" si="12">+BB4+BC3</f>
+        <v>7280.8596875000003</v>
+      </c>
+      <c r="BD4" s="2">
+        <f t="shared" ref="BD4" si="13">+BC4+BD3</f>
+        <v>8080.8596875000003</v>
+      </c>
+      <c r="BE4" s="2">
+        <f t="shared" ref="BE4" si="14">+BD4+BE3</f>
+        <v>8880.8596875000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
@@ -2551,8 +2583,12 @@
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
-    </row>
-    <row r="6" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+    </row>
+    <row r="6" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>54</v>
       </c>
@@ -2602,52 +2638,53 @@
         <v>131.5</v>
       </c>
       <c r="Z6" s="2">
-        <v>100</v>
-      </c>
-      <c r="AO6" s="2">
+        <v>110.4</v>
+      </c>
+      <c r="AS6" s="2">
         <f>SUM(O6:R6)</f>
         <v>200.29999999999998</v>
       </c>
-      <c r="AP6" s="2">
+      <c r="AT6" s="2">
         <f>SUM(S6:V6)</f>
         <v>820.85699999999997</v>
       </c>
-      <c r="AQ6" s="2">
+      <c r="AU6" s="2">
         <f>SUM(W6:Z6)</f>
-        <v>888.351</v>
-      </c>
-      <c r="AR6" s="2">
-        <v>50</v>
-      </c>
-      <c r="AS6" s="2">
+        <v>898.75099999999998</v>
+      </c>
+      <c r="AV6" s="2">
+        <f>SUM(W6:Z6)</f>
+        <v>898.75099999999998</v>
+      </c>
+      <c r="AW6" s="2">
         <v>100</v>
       </c>
-      <c r="AT6" s="2">
+      <c r="AX6" s="2">
         <v>150</v>
       </c>
-      <c r="AU6" s="2">
+      <c r="AY6" s="2">
         <v>200</v>
       </c>
-      <c r="AV6" s="2">
+      <c r="AZ6" s="2">
         <v>250</v>
-      </c>
-      <c r="AW6" s="2">
-        <v>300</v>
-      </c>
-      <c r="AX6" s="2">
-        <v>300</v>
-      </c>
-      <c r="AY6" s="2">
-        <v>300</v>
-      </c>
-      <c r="AZ6" s="2">
-        <v>300</v>
       </c>
       <c r="BA6" s="2">
         <v>300</v>
       </c>
-    </row>
-    <row r="7" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BB6" s="2">
+        <v>300</v>
+      </c>
+      <c r="BC6" s="2">
+        <v>300</v>
+      </c>
+      <c r="BD6" s="2">
+        <v>300</v>
+      </c>
+      <c r="BE6" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>55</v>
       </c>
@@ -2699,91 +2736,90 @@
         <v>238.5</v>
       </c>
       <c r="Z7" s="2">
-        <f>+V7*0.8</f>
-        <v>203.20000000000002</v>
-      </c>
-      <c r="AH7" s="2">
-        <f t="shared" ref="AH7:AN7" si="15">+AH13</f>
+        <v>259.2</v>
+      </c>
+      <c r="AL7" s="2">
+        <f t="shared" ref="AL7:AR7" si="15">+AL13</f>
         <v>5.4</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AM7" s="2">
         <f t="shared" si="15"/>
         <v>155</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AN7" s="2">
         <f t="shared" si="15"/>
         <v>301</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AO7" s="2">
         <f t="shared" si="15"/>
         <v>381</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AP7" s="2">
         <f t="shared" si="15"/>
         <v>456</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AQ7" s="2">
         <f t="shared" si="15"/>
         <v>612</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AR7" s="2">
         <f t="shared" si="15"/>
         <v>844</v>
       </c>
-      <c r="AO7" s="2">
-        <f t="shared" ref="AO7" si="16">SUM(O7:R7)</f>
+      <c r="AS7" s="2">
+        <f t="shared" ref="AS7" si="16">SUM(O7:R7)</f>
         <v>944.57600000000002</v>
       </c>
-      <c r="AP7" s="2">
-        <f t="shared" ref="AP7" si="17">SUM(S7:V7)</f>
+      <c r="AT7" s="2">
+        <f t="shared" ref="AT7" si="17">SUM(S7:V7)</f>
         <v>967.17499999999995</v>
       </c>
-      <c r="AQ7" s="2">
-        <f t="shared" ref="AQ7" si="18">SUM(W7:Z7)</f>
-        <v>909.97199999999998</v>
-      </c>
-      <c r="AR7" s="2">
-        <f>+AQ7*0.99</f>
-        <v>900.87227999999993</v>
-      </c>
-      <c r="AS7" s="2">
-        <f t="shared" ref="AS7:BA7" si="19">+AR7*0.99</f>
-        <v>891.86355719999995</v>
-      </c>
-      <c r="AT7" s="2">
-        <f t="shared" si="19"/>
-        <v>882.94492162799997</v>
-      </c>
       <c r="AU7" s="2">
-        <f t="shared" si="19"/>
-        <v>874.11547241172002</v>
+        <f t="shared" ref="AU7" si="18">SUM(W7:Z7)</f>
+        <v>965.97199999999998</v>
       </c>
       <c r="AV7" s="2">
-        <f t="shared" si="19"/>
-        <v>865.3743176876028</v>
+        <f>SUM(W7:Z7)</f>
+        <v>965.97199999999998</v>
       </c>
       <c r="AW7" s="2">
-        <f t="shared" si="19"/>
-        <v>856.72057451072681</v>
+        <f t="shared" ref="AW7:BE7" si="19">+AV7*0.99</f>
+        <v>956.31227999999999</v>
       </c>
       <c r="AX7" s="2">
         <f t="shared" si="19"/>
-        <v>848.15336876561958</v>
+        <v>946.74915720000001</v>
       </c>
       <c r="AY7" s="2">
         <f t="shared" si="19"/>
-        <v>839.67183507796335</v>
+        <v>937.28166562800004</v>
       </c>
       <c r="AZ7" s="2">
         <f t="shared" si="19"/>
-        <v>831.27511672718367</v>
+        <v>927.90884897171998</v>
       </c>
       <c r="BA7" s="2">
         <f t="shared" si="19"/>
-        <v>822.96236555991186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>918.62976048200278</v>
+      </c>
+      <c r="BB7" s="2">
+        <f t="shared" si="19"/>
+        <v>909.4434628771827</v>
+      </c>
+      <c r="BC7" s="2">
+        <f t="shared" si="19"/>
+        <v>900.34902824841083</v>
+      </c>
+      <c r="BD7" s="2">
+        <f t="shared" si="19"/>
+        <v>891.34553796592672</v>
+      </c>
+      <c r="BE7" s="2">
+        <f t="shared" si="19"/>
+        <v>882.43208258626748</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="17" t="s">
         <v>41</v>
       </c>
@@ -2807,7 +2843,7 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
@@ -2831,7 +2867,7 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
@@ -2855,7 +2891,7 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
@@ -2922,62 +2958,62 @@
       </c>
       <c r="Z11" s="2">
         <f>+Z7+Z6</f>
-        <v>303.20000000000005</v>
-      </c>
-      <c r="AO11" s="2">
-        <f t="shared" ref="AO11:AP11" si="20">+AO7+AO6</f>
+        <v>369.6</v>
+      </c>
+      <c r="AS11" s="2">
+        <f t="shared" ref="AS11:AT11" si="20">+AS7+AS6</f>
         <v>1144.876</v>
       </c>
-      <c r="AP11" s="2">
+      <c r="AT11" s="2">
         <f t="shared" si="20"/>
         <v>1788.0319999999999</v>
       </c>
-      <c r="AQ11" s="2">
-        <f>+AQ7+AQ6</f>
-        <v>1798.3229999999999</v>
-      </c>
-      <c r="AR11" s="2">
-        <f t="shared" ref="AR11:BA11" si="21">+AR7+AR6</f>
-        <v>950.87227999999993</v>
-      </c>
-      <c r="AS11" s="2">
-        <f t="shared" si="21"/>
-        <v>991.86355719999995</v>
-      </c>
-      <c r="AT11" s="2">
-        <f t="shared" si="21"/>
-        <v>1032.944921628</v>
-      </c>
       <c r="AU11" s="2">
-        <f t="shared" si="21"/>
-        <v>1074.11547241172</v>
+        <f>+AU7+AU6</f>
+        <v>1864.723</v>
       </c>
       <c r="AV11" s="2">
-        <f t="shared" si="21"/>
-        <v>1115.3743176876028</v>
+        <f t="shared" ref="AV11:BE11" si="21">+AV7+AV6</f>
+        <v>1864.723</v>
       </c>
       <c r="AW11" s="2">
         <f t="shared" si="21"/>
-        <v>1156.7205745107267</v>
+        <v>1056.3122800000001</v>
       </c>
       <c r="AX11" s="2">
         <f t="shared" si="21"/>
-        <v>1148.1533687656197</v>
+        <v>1096.7491571999999</v>
       </c>
       <c r="AY11" s="2">
         <f t="shared" si="21"/>
-        <v>1139.6718350779634</v>
+        <v>1137.2816656280002</v>
       </c>
       <c r="AZ11" s="2">
         <f t="shared" si="21"/>
-        <v>1131.2751167271836</v>
+        <v>1177.9088489717201</v>
       </c>
       <c r="BA11" s="2">
         <f t="shared" si="21"/>
-        <v>1122.9623655599119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>1218.6297604820029</v>
+      </c>
+      <c r="BB11" s="2">
+        <f t="shared" si="21"/>
+        <v>1209.4434628771828</v>
+      </c>
+      <c r="BC11" s="2">
+        <f t="shared" si="21"/>
+        <v>1200.3490282484108</v>
+      </c>
+      <c r="BD11" s="2">
+        <f t="shared" si="21"/>
+        <v>1191.3455379659267</v>
+      </c>
+      <c r="BE11" s="2">
+        <f t="shared" si="21"/>
+        <v>1182.4320825862674</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
@@ -3037,7 +3073,7 @@
         <v>29.312999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:53" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:57" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>10</v>
       </c>
@@ -3108,83 +3144,83 @@
       </c>
       <c r="Z13" s="6">
         <f t="shared" si="22"/>
-        <v>332.51300000000003</v>
-      </c>
-      <c r="AH13" s="6">
+        <v>398.91300000000001</v>
+      </c>
+      <c r="AL13" s="6">
         <v>5.4</v>
       </c>
-      <c r="AI13" s="6">
+      <c r="AM13" s="6">
         <v>155</v>
       </c>
-      <c r="AJ13" s="6">
+      <c r="AN13" s="6">
         <v>301</v>
       </c>
-      <c r="AK13" s="6">
+      <c r="AO13" s="6">
         <v>381</v>
       </c>
-      <c r="AL13" s="6">
+      <c r="AP13" s="6">
         <v>456</v>
       </c>
-      <c r="AM13" s="6">
+      <c r="AQ13" s="6">
         <v>612</v>
       </c>
-      <c r="AN13" s="6">
+      <c r="AR13" s="6">
         <v>844</v>
       </c>
-      <c r="AO13" s="6">
-        <f t="shared" ref="AO13:AQ13" si="23">+AO11+AO12</f>
+      <c r="AS13" s="6">
+        <f t="shared" ref="AS13:AU13" si="23">+AS11+AS12</f>
         <v>1144.876</v>
       </c>
-      <c r="AP13" s="6">
+      <c r="AT13" s="6">
         <f t="shared" si="23"/>
         <v>1788.0319999999999</v>
       </c>
-      <c r="AQ13" s="6">
+      <c r="AU13" s="6">
         <f t="shared" si="23"/>
-        <v>1798.3229999999999</v>
-      </c>
-      <c r="AR13" s="6">
-        <f t="shared" ref="AR13:BA13" si="24">+AR11+AR12</f>
-        <v>950.87227999999993</v>
-      </c>
-      <c r="AS13" s="6">
-        <f t="shared" si="24"/>
-        <v>991.86355719999995</v>
-      </c>
-      <c r="AT13" s="6">
-        <f t="shared" si="24"/>
-        <v>1032.944921628</v>
-      </c>
-      <c r="AU13" s="6">
-        <f t="shared" si="24"/>
-        <v>1074.11547241172</v>
+        <v>1864.723</v>
       </c>
       <c r="AV13" s="6">
-        <f t="shared" si="24"/>
-        <v>1115.3743176876028</v>
+        <f t="shared" ref="AV13:BE13" si="24">+AV11+AV12</f>
+        <v>1864.723</v>
       </c>
       <c r="AW13" s="6">
         <f t="shared" si="24"/>
-        <v>1156.7205745107267</v>
+        <v>1056.3122800000001</v>
       </c>
       <c r="AX13" s="6">
         <f t="shared" si="24"/>
-        <v>1148.1533687656197</v>
+        <v>1096.7491571999999</v>
       </c>
       <c r="AY13" s="6">
         <f t="shared" si="24"/>
-        <v>1139.6718350779634</v>
+        <v>1137.2816656280002</v>
       </c>
       <c r="AZ13" s="6">
         <f t="shared" si="24"/>
-        <v>1131.2751167271836</v>
+        <v>1177.9088489717201</v>
       </c>
       <c r="BA13" s="6">
         <f t="shared" si="24"/>
-        <v>1122.9623655599119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>1218.6297604820029</v>
+      </c>
+      <c r="BB13" s="6">
+        <f t="shared" si="24"/>
+        <v>1209.4434628771828</v>
+      </c>
+      <c r="BC13" s="6">
+        <f t="shared" si="24"/>
+        <v>1200.3490282484108</v>
+      </c>
+      <c r="BD13" s="6">
+        <f t="shared" si="24"/>
+        <v>1191.3455379659267</v>
+      </c>
+      <c r="BE13" s="6">
+        <f t="shared" si="24"/>
+        <v>1182.4320825862674</v>
+      </c>
+    </row>
+    <row r="14" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
@@ -3241,62 +3277,62 @@
       </c>
       <c r="Z14" s="2">
         <f>+Z13*0.18</f>
-        <v>59.852340000000005</v>
-      </c>
-      <c r="AO14" s="2">
-        <f t="shared" ref="AO14:AO17" si="25">SUM(O14:R14)</f>
+        <v>71.804339999999996</v>
+      </c>
+      <c r="AS14" s="2">
+        <f t="shared" ref="AS14:AS17" si="25">SUM(O14:R14)</f>
         <v>150.34300000000002</v>
       </c>
-      <c r="AP14" s="2">
-        <f t="shared" ref="AP14:AP17" si="26">SUM(S14:V14)</f>
+      <c r="AT14" s="2">
+        <f t="shared" ref="AT14:AT17" si="26">SUM(S14:V14)</f>
         <v>319.09900000000005</v>
       </c>
-      <c r="AQ14" s="2">
-        <f t="shared" ref="AQ14" si="27">SUM(W14:Z14)</f>
-        <v>500.74933999999996</v>
-      </c>
-      <c r="AR14" s="2">
-        <f>+AR13-AR15</f>
-        <v>142.63084200000003</v>
-      </c>
-      <c r="AS14" s="2">
-        <f t="shared" ref="AS14:BA14" si="28">+AS13-AS15</f>
-        <v>148.77953358000002</v>
-      </c>
-      <c r="AT14" s="2">
-        <f t="shared" si="28"/>
-        <v>154.9417382442</v>
-      </c>
       <c r="AU14" s="2">
-        <f t="shared" si="28"/>
-        <v>161.117320861758</v>
+        <f t="shared" ref="AU14" si="27">SUM(W14:Z14)</f>
+        <v>512.70133999999996</v>
       </c>
       <c r="AV14" s="2">
-        <f t="shared" si="28"/>
-        <v>167.30614765314044</v>
+        <f>+AV13-AV15</f>
+        <v>279.70845000000008</v>
       </c>
       <c r="AW14" s="2">
-        <f t="shared" si="28"/>
-        <v>173.50808617660903</v>
+        <f t="shared" ref="AW14:BE14" si="28">+AW13-AW15</f>
+        <v>158.44684200000006</v>
       </c>
       <c r="AX14" s="2">
         <f t="shared" si="28"/>
-        <v>172.22300531484302</v>
+        <v>164.51237358000003</v>
       </c>
       <c r="AY14" s="2">
         <f t="shared" si="28"/>
-        <v>170.9507752616945</v>
+        <v>170.59224984420007</v>
       </c>
       <c r="AZ14" s="2">
         <f t="shared" si="28"/>
-        <v>169.69126750907753</v>
+        <v>176.68632734575806</v>
       </c>
       <c r="BA14" s="2">
         <f t="shared" si="28"/>
-        <v>168.44435483398684</v>
-      </c>
-    </row>
-    <row r="15" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>182.79446407230057</v>
+      </c>
+      <c r="BB14" s="2">
+        <f t="shared" si="28"/>
+        <v>181.4165194315774</v>
+      </c>
+      <c r="BC14" s="2">
+        <f t="shared" si="28"/>
+        <v>180.05235423726162</v>
+      </c>
+      <c r="BD14" s="2">
+        <f t="shared" si="28"/>
+        <v>178.70183069488905</v>
+      </c>
+      <c r="BE14" s="2">
+        <f t="shared" si="28"/>
+        <v>177.36481238794011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
@@ -3367,62 +3403,62 @@
       </c>
       <c r="Z15" s="2">
         <f t="shared" si="30"/>
-        <v>272.66066000000001</v>
-      </c>
-      <c r="AO15" s="2">
-        <f>+AO13-AO14</f>
+        <v>327.10865999999999</v>
+      </c>
+      <c r="AS15" s="2">
+        <f>+AS13-AS14</f>
         <v>994.5329999999999</v>
       </c>
-      <c r="AP15" s="2">
-        <f>+AP13-AP14</f>
+      <c r="AT15" s="2">
+        <f>+AT13-AT14</f>
         <v>1468.933</v>
       </c>
-      <c r="AQ15" s="2">
-        <f>+AQ13-AQ14</f>
-        <v>1297.57366</v>
-      </c>
-      <c r="AR15" s="2">
-        <f>+AR13*0.85</f>
-        <v>808.2414379999999</v>
-      </c>
-      <c r="AS15" s="2">
-        <f t="shared" ref="AS15:BA15" si="31">+AS13*0.85</f>
-        <v>843.08402361999993</v>
-      </c>
-      <c r="AT15" s="2">
-        <f t="shared" si="31"/>
-        <v>878.00318338379998</v>
-      </c>
       <c r="AU15" s="2">
-        <f t="shared" si="31"/>
-        <v>912.99815154996202</v>
+        <f>+AU13-AU14</f>
+        <v>1352.0216599999999</v>
       </c>
       <c r="AV15" s="2">
-        <f t="shared" si="31"/>
-        <v>948.06817003446236</v>
+        <f>+AV13*0.85</f>
+        <v>1585.0145499999999</v>
       </c>
       <c r="AW15" s="2">
-        <f t="shared" si="31"/>
-        <v>983.21248833411767</v>
+        <f t="shared" ref="AW15:BE15" si="31">+AW13*0.85</f>
+        <v>897.86543800000004</v>
       </c>
       <c r="AX15" s="2">
         <f t="shared" si="31"/>
-        <v>975.93036345077667</v>
+        <v>932.23678361999987</v>
       </c>
       <c r="AY15" s="2">
         <f t="shared" si="31"/>
-        <v>968.72105981626885</v>
+        <v>966.68941578380009</v>
       </c>
       <c r="AZ15" s="2">
         <f t="shared" si="31"/>
-        <v>961.58384921810602</v>
+        <v>1001.222521625962</v>
       </c>
       <c r="BA15" s="2">
         <f t="shared" si="31"/>
-        <v>954.51801072592502</v>
-      </c>
-    </row>
-    <row r="16" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>1035.8352964097023</v>
+      </c>
+      <c r="BB15" s="2">
+        <f t="shared" si="31"/>
+        <v>1028.0269434456054</v>
+      </c>
+      <c r="BC15" s="2">
+        <f t="shared" si="31"/>
+        <v>1020.2966740111492</v>
+      </c>
+      <c r="BD15" s="2">
+        <f t="shared" si="31"/>
+        <v>1012.6437072710377</v>
+      </c>
+      <c r="BE15" s="2">
+        <f t="shared" si="31"/>
+        <v>1005.0672701983273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>26</v>
       </c>
@@ -3478,16 +3514,16 @@
       <c r="Y16" s="2">
         <v>218.89</v>
       </c>
-      <c r="AO16" s="2">
+      <c r="AS16" s="2">
         <f t="shared" si="25"/>
         <v>877.38699999999994</v>
       </c>
-      <c r="AP16" s="2">
+      <c r="AT16" s="2">
         <f t="shared" si="26"/>
         <v>780.20299999999997</v>
       </c>
     </row>
-    <row r="17" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
@@ -3542,60 +3578,60 @@
       <c r="Y17" s="2">
         <v>91.893000000000001</v>
       </c>
-      <c r="AO17" s="2">
+      <c r="AS17" s="2">
         <f t="shared" si="25"/>
         <v>481.87099999999998</v>
       </c>
-      <c r="AP17" s="2">
+      <c r="AT17" s="2">
         <f t="shared" si="26"/>
         <v>558.47199999999998</v>
       </c>
-      <c r="AQ17" s="2">
-        <f>+AP17</f>
+      <c r="AU17" s="2">
+        <f>+AT17</f>
         <v>558.47199999999998</v>
       </c>
-      <c r="AR17" s="2">
-        <f>+AQ17*0.9</f>
+      <c r="AV17" s="2">
+        <f>+AU17*0.9</f>
         <v>502.62479999999999</v>
       </c>
-      <c r="AS17" s="2">
-        <f t="shared" ref="AS17:BA17" si="32">+AR17*0.9</f>
+      <c r="AW17" s="2">
+        <f t="shared" ref="AW17:BE17" si="32">+AV17*0.9</f>
         <v>452.36232000000001</v>
       </c>
-      <c r="AT17" s="2">
+      <c r="AX17" s="2">
         <f t="shared" si="32"/>
         <v>407.12608800000004</v>
       </c>
-      <c r="AU17" s="2">
+      <c r="AY17" s="2">
         <f t="shared" si="32"/>
         <v>366.41347920000004</v>
       </c>
-      <c r="AV17" s="2">
+      <c r="AZ17" s="2">
         <f t="shared" si="32"/>
         <v>329.77213128000005</v>
       </c>
-      <c r="AW17" s="2">
+      <c r="BA17" s="2">
         <f t="shared" si="32"/>
         <v>296.79491815200004</v>
       </c>
-      <c r="AX17" s="2">
+      <c r="BB17" s="2">
         <f t="shared" si="32"/>
         <v>267.11542633680006</v>
       </c>
-      <c r="AY17" s="2">
+      <c r="BC17" s="2">
         <f t="shared" si="32"/>
         <v>240.40388370312004</v>
       </c>
-      <c r="AZ17" s="2">
+      <c r="BD17" s="2">
         <f t="shared" si="32"/>
         <v>216.36349533280804</v>
       </c>
-      <c r="BA17" s="2">
+      <c r="BE17" s="2">
         <f t="shared" si="32"/>
         <v>194.72714579952725</v>
       </c>
     </row>
-    <row r="18" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
@@ -3668,60 +3704,60 @@
         <f>+Z17+Z16</f>
         <v>0</v>
       </c>
-      <c r="AO18" s="2">
-        <f>+AO16+AO17</f>
+      <c r="AS18" s="2">
+        <f>+AS16+AS17</f>
         <v>1359.2579999999998</v>
       </c>
-      <c r="AP18" s="2">
-        <f>+AP16+AP17</f>
+      <c r="AT18" s="2">
+        <f>+AT16+AT17</f>
         <v>1338.675</v>
       </c>
-      <c r="AQ18" s="2">
-        <f>+AQ16+AQ17</f>
+      <c r="AU18" s="2">
+        <f>+AU16+AU17</f>
         <v>558.47199999999998</v>
       </c>
-      <c r="AR18" s="2">
-        <f t="shared" ref="AR18" si="35">+AR16+AR17</f>
+      <c r="AV18" s="2">
+        <f t="shared" ref="AV18" si="35">+AV16+AV17</f>
         <v>502.62479999999999</v>
       </c>
-      <c r="AS18" s="2">
-        <f t="shared" ref="AS18" si="36">+AS16+AS17</f>
+      <c r="AW18" s="2">
+        <f t="shared" ref="AW18" si="36">+AW16+AW17</f>
         <v>452.36232000000001</v>
       </c>
-      <c r="AT18" s="2">
-        <f t="shared" ref="AT18" si="37">+AT16+AT17</f>
+      <c r="AX18" s="2">
+        <f t="shared" ref="AX18" si="37">+AX16+AX17</f>
         <v>407.12608800000004</v>
       </c>
-      <c r="AU18" s="2">
-        <f t="shared" ref="AU18" si="38">+AU16+AU17</f>
+      <c r="AY18" s="2">
+        <f t="shared" ref="AY18" si="38">+AY16+AY17</f>
         <v>366.41347920000004</v>
       </c>
-      <c r="AV18" s="2">
-        <f t="shared" ref="AV18" si="39">+AV16+AV17</f>
+      <c r="AZ18" s="2">
+        <f t="shared" ref="AZ18" si="39">+AZ16+AZ17</f>
         <v>329.77213128000005</v>
       </c>
-      <c r="AW18" s="2">
-        <f t="shared" ref="AW18" si="40">+AW16+AW17</f>
+      <c r="BA18" s="2">
+        <f t="shared" ref="BA18" si="40">+BA16+BA17</f>
         <v>296.79491815200004</v>
       </c>
-      <c r="AX18" s="2">
-        <f t="shared" ref="AX18" si="41">+AX16+AX17</f>
+      <c r="BB18" s="2">
+        <f t="shared" ref="BB18" si="41">+BB16+BB17</f>
         <v>267.11542633680006</v>
       </c>
-      <c r="AY18" s="2">
-        <f t="shared" ref="AY18" si="42">+AY16+AY17</f>
+      <c r="BC18" s="2">
+        <f t="shared" ref="BC18" si="42">+BC16+BC17</f>
         <v>240.40388370312004</v>
       </c>
-      <c r="AZ18" s="2">
-        <f t="shared" ref="AZ18" si="43">+AZ16+AZ17</f>
+      <c r="BD18" s="2">
+        <f t="shared" ref="BD18" si="43">+BD16+BD17</f>
         <v>216.36349533280804</v>
       </c>
-      <c r="BA18" s="2">
-        <f t="shared" ref="BA18" si="44">+BA16+BA17</f>
+      <c r="BE18" s="2">
+        <f t="shared" ref="BE18" si="44">+BE16+BE17</f>
         <v>194.72714579952725</v>
       </c>
     </row>
-    <row r="19" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
@@ -3792,62 +3828,62 @@
       </c>
       <c r="Z19" s="2">
         <f>+Z15-Z18</f>
-        <v>272.66066000000001</v>
-      </c>
-      <c r="AO19" s="2">
-        <f>+AO15-AO18</f>
+        <v>327.10865999999999</v>
+      </c>
+      <c r="AS19" s="2">
+        <f>+AS15-AS18</f>
         <v>-364.72499999999991</v>
       </c>
-      <c r="AP19" s="2">
-        <f>+AP15-AP18</f>
+      <c r="AT19" s="2">
+        <f>+AT15-AT18</f>
         <v>130.25800000000004</v>
       </c>
-      <c r="AQ19" s="2">
-        <f>+AQ15-AQ18</f>
-        <v>739.10166000000004</v>
-      </c>
-      <c r="AR19" s="2">
-        <f t="shared" ref="AR19" si="47">+AR15-AR18</f>
-        <v>305.61663799999991</v>
-      </c>
-      <c r="AS19" s="2">
-        <f t="shared" ref="AS19" si="48">+AS15-AS18</f>
-        <v>390.72170361999991</v>
-      </c>
-      <c r="AT19" s="2">
-        <f t="shared" ref="AT19" si="49">+AT15-AT18</f>
-        <v>470.87709538379994</v>
-      </c>
       <c r="AU19" s="2">
-        <f t="shared" ref="AU19" si="50">+AU15-AU18</f>
-        <v>546.58467234996192</v>
+        <f>+AU15-AU18</f>
+        <v>793.5496599999999</v>
       </c>
       <c r="AV19" s="2">
-        <f t="shared" ref="AV19" si="51">+AV15-AV18</f>
-        <v>618.2960387544623</v>
+        <f t="shared" ref="AV19" si="47">+AV15-AV18</f>
+        <v>1082.3897499999998</v>
       </c>
       <c r="AW19" s="2">
-        <f t="shared" ref="AW19" si="52">+AW15-AW18</f>
-        <v>686.41757018211763</v>
+        <f t="shared" ref="AW19" si="48">+AW15-AW18</f>
+        <v>445.50311800000003</v>
       </c>
       <c r="AX19" s="2">
-        <f t="shared" ref="AX19" si="53">+AX15-AX18</f>
-        <v>708.81493711397661</v>
+        <f t="shared" ref="AX19" si="49">+AX15-AX18</f>
+        <v>525.11069561999989</v>
       </c>
       <c r="AY19" s="2">
-        <f t="shared" ref="AY19" si="54">+AY15-AY18</f>
-        <v>728.31717611314878</v>
+        <f t="shared" ref="AY19" si="50">+AY15-AY18</f>
+        <v>600.2759365838001</v>
       </c>
       <c r="AZ19" s="2">
-        <f t="shared" ref="AZ19" si="55">+AZ15-AZ18</f>
-        <v>745.22035388529798</v>
+        <f t="shared" ref="AZ19" si="51">+AZ15-AZ18</f>
+        <v>671.45039034596198</v>
       </c>
       <c r="BA19" s="2">
-        <f t="shared" ref="BA19" si="56">+BA15-BA18</f>
-        <v>759.79086492639772</v>
-      </c>
-    </row>
-    <row r="20" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BA19" si="52">+BA15-BA18</f>
+        <v>739.04037825770229</v>
+      </c>
+      <c r="BB19" s="2">
+        <f t="shared" ref="BB19" si="53">+BB15-BB18</f>
+        <v>760.91151710880536</v>
+      </c>
+      <c r="BC19" s="2">
+        <f t="shared" ref="BC19" si="54">+BC15-BC18</f>
+        <v>779.89279030802913</v>
+      </c>
+      <c r="BD19" s="2">
+        <f t="shared" ref="BD19" si="55">+BD15-BD18</f>
+        <v>796.28021193822963</v>
+      </c>
+      <c r="BE19" s="2">
+        <f t="shared" ref="BE19" si="56">+BE15-BE18</f>
+        <v>810.34012439880007</v>
+      </c>
+    </row>
+    <row r="20" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
@@ -3902,16 +3938,16 @@
       <c r="Y20" s="2">
         <v>0</v>
       </c>
-      <c r="AO20" s="2">
-        <f t="shared" ref="AO20" si="57">SUM(O20:R20)</f>
+      <c r="AS20" s="2">
+        <f t="shared" ref="AS20" si="57">SUM(O20:R20)</f>
         <v>33.055</v>
       </c>
-      <c r="AP20" s="2">
-        <f t="shared" ref="AP20" si="58">SUM(S20:V20)</f>
+      <c r="AT20" s="2">
+        <f t="shared" ref="AT20" si="58">SUM(S20:V20)</f>
         <v>42.692999999999998</v>
       </c>
     </row>
-    <row r="21" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
@@ -3982,62 +4018,62 @@
       </c>
       <c r="Z21" s="2">
         <f>+Z19+Z20</f>
-        <v>272.66066000000001</v>
-      </c>
-      <c r="AO21" s="2">
-        <f>+AO19+AO20</f>
+        <v>327.10865999999999</v>
+      </c>
+      <c r="AS21" s="2">
+        <f>+AS19+AS20</f>
         <v>-331.6699999999999</v>
       </c>
-      <c r="AP21" s="2">
-        <f>+AP19+AP20</f>
+      <c r="AT21" s="2">
+        <f>+AT19+AT20</f>
         <v>172.95100000000002</v>
       </c>
-      <c r="AQ21" s="2">
-        <f>+AQ19+AQ20</f>
-        <v>739.10166000000004</v>
-      </c>
-      <c r="AR21" s="2">
-        <f t="shared" ref="AR21:BA21" si="60">+AR19+AR20</f>
-        <v>305.61663799999991</v>
-      </c>
-      <c r="AS21" s="2">
-        <f t="shared" si="60"/>
-        <v>390.72170361999991</v>
-      </c>
-      <c r="AT21" s="2">
-        <f t="shared" si="60"/>
-        <v>470.87709538379994</v>
-      </c>
       <c r="AU21" s="2">
-        <f t="shared" si="60"/>
-        <v>546.58467234996192</v>
+        <f>+AU19+AU20</f>
+        <v>793.5496599999999</v>
       </c>
       <c r="AV21" s="2">
-        <f t="shared" si="60"/>
-        <v>618.2960387544623</v>
+        <f t="shared" ref="AV21:BE21" si="60">+AV19+AV20</f>
+        <v>1082.3897499999998</v>
       </c>
       <c r="AW21" s="2">
         <f t="shared" si="60"/>
-        <v>686.41757018211763</v>
+        <v>445.50311800000003</v>
       </c>
       <c r="AX21" s="2">
         <f t="shared" si="60"/>
-        <v>708.81493711397661</v>
+        <v>525.11069561999989</v>
       </c>
       <c r="AY21" s="2">
         <f t="shared" si="60"/>
-        <v>728.31717611314878</v>
+        <v>600.2759365838001</v>
       </c>
       <c r="AZ21" s="2">
         <f t="shared" si="60"/>
-        <v>745.22035388529798</v>
+        <v>671.45039034596198</v>
       </c>
       <c r="BA21" s="2">
         <f t="shared" si="60"/>
-        <v>759.79086492639772</v>
-      </c>
-    </row>
-    <row r="22" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>739.04037825770229</v>
+      </c>
+      <c r="BB21" s="2">
+        <f t="shared" si="60"/>
+        <v>760.91151710880536</v>
+      </c>
+      <c r="BC21" s="2">
+        <f t="shared" si="60"/>
+        <v>779.89279030802913</v>
+      </c>
+      <c r="BD21" s="2">
+        <f t="shared" si="60"/>
+        <v>796.28021193822963</v>
+      </c>
+      <c r="BE21" s="2">
+        <f t="shared" si="60"/>
+        <v>810.34012439880007</v>
+      </c>
+    </row>
+    <row r="22" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>30</v>
       </c>
@@ -4095,60 +4131,60 @@
       <c r="Z22" s="2">
         <v>0</v>
       </c>
-      <c r="AO22" s="2">
-        <f t="shared" ref="AO22" si="61">SUM(O22:R22)</f>
+      <c r="AS22" s="2">
+        <f t="shared" ref="AS22" si="61">SUM(O22:R22)</f>
         <v>15.879000000000001</v>
       </c>
-      <c r="AP22" s="2">
-        <f t="shared" ref="AP22" si="62">SUM(S22:V22)</f>
+      <c r="AT22" s="2">
+        <f t="shared" ref="AT22" si="62">SUM(S22:V22)</f>
         <v>25.535</v>
       </c>
-      <c r="AQ22" s="2">
-        <f>+AQ21*0.2</f>
-        <v>147.82033200000001</v>
-      </c>
-      <c r="AR22" s="2">
-        <f t="shared" ref="AR22:BA22" si="63">+AR21*0.2</f>
-        <v>61.123327599999982</v>
-      </c>
-      <c r="AS22" s="2">
-        <f t="shared" si="63"/>
-        <v>78.144340723999989</v>
-      </c>
-      <c r="AT22" s="2">
-        <f t="shared" si="63"/>
-        <v>94.175419076759994</v>
-      </c>
       <c r="AU22" s="2">
-        <f t="shared" si="63"/>
-        <v>109.31693446999239</v>
+        <f>+AU21*0.2</f>
+        <v>158.70993199999998</v>
       </c>
       <c r="AV22" s="2">
-        <f t="shared" si="63"/>
-        <v>123.65920775089246</v>
+        <f t="shared" ref="AV22:BE22" si="63">+AV21*0.2</f>
+        <v>216.47794999999996</v>
       </c>
       <c r="AW22" s="2">
         <f t="shared" si="63"/>
-        <v>137.28351403642353</v>
+        <v>89.100623600000006</v>
       </c>
       <c r="AX22" s="2">
         <f t="shared" si="63"/>
-        <v>141.76298742279533</v>
+        <v>105.02213912399998</v>
       </c>
       <c r="AY22" s="2">
         <f t="shared" si="63"/>
-        <v>145.66343522262977</v>
+        <v>120.05518731676003</v>
       </c>
       <c r="AZ22" s="2">
         <f t="shared" si="63"/>
-        <v>149.0440707770596</v>
+        <v>134.29007806919239</v>
       </c>
       <c r="BA22" s="2">
         <f t="shared" si="63"/>
-        <v>151.95817298527956</v>
-      </c>
-    </row>
-    <row r="23" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>147.80807565154046</v>
+      </c>
+      <c r="BB22" s="2">
+        <f t="shared" si="63"/>
+        <v>152.18230342176108</v>
+      </c>
+      <c r="BC22" s="2">
+        <f t="shared" si="63"/>
+        <v>155.97855806160584</v>
+      </c>
+      <c r="BD22" s="2">
+        <f t="shared" si="63"/>
+        <v>159.25604238764595</v>
+      </c>
+      <c r="BE22" s="2">
+        <f t="shared" si="63"/>
+        <v>162.06802487976003</v>
+      </c>
+    </row>
+    <row r="23" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>31</v>
       </c>
@@ -4219,62 +4255,62 @@
       </c>
       <c r="Z23" s="2">
         <f>+Z21-Z22</f>
-        <v>272.66066000000001</v>
-      </c>
-      <c r="AO23" s="2">
-        <f>+AO21-AO22</f>
+        <v>327.10865999999999</v>
+      </c>
+      <c r="AS23" s="2">
+        <f>+AS21-AS22</f>
         <v>-347.54899999999992</v>
       </c>
-      <c r="AP23" s="2">
-        <f>+AP21-AP22</f>
+      <c r="AT23" s="2">
+        <f>+AT21-AT22</f>
         <v>147.41600000000003</v>
       </c>
-      <c r="AQ23" s="2">
-        <f>+AQ21-AQ22</f>
-        <v>591.28132800000003</v>
-      </c>
-      <c r="AR23" s="2">
-        <f t="shared" ref="AR23:BA23" si="65">+AR21-AR22</f>
-        <v>244.49331039999993</v>
-      </c>
-      <c r="AS23" s="2">
-        <f t="shared" si="65"/>
-        <v>312.57736289599995</v>
-      </c>
-      <c r="AT23" s="2">
-        <f t="shared" si="65"/>
-        <v>376.70167630703997</v>
-      </c>
       <c r="AU23" s="2">
-        <f t="shared" si="65"/>
-        <v>437.26773787996956</v>
+        <f>+AU21-AU22</f>
+        <v>634.83972799999992</v>
       </c>
       <c r="AV23" s="2">
-        <f t="shared" si="65"/>
-        <v>494.63683100356985</v>
+        <f t="shared" ref="AV23:BE23" si="65">+AV21-AV22</f>
+        <v>865.91179999999986</v>
       </c>
       <c r="AW23" s="2">
         <f t="shared" si="65"/>
-        <v>549.1340561456941</v>
+        <v>356.40249440000002</v>
       </c>
       <c r="AX23" s="2">
         <f t="shared" si="65"/>
-        <v>567.05194969118133</v>
+        <v>420.08855649599991</v>
       </c>
       <c r="AY23" s="2">
         <f t="shared" si="65"/>
-        <v>582.65374089051897</v>
+        <v>480.22074926704011</v>
       </c>
       <c r="AZ23" s="2">
         <f t="shared" si="65"/>
-        <v>596.17628310823841</v>
+        <v>537.16031227676956</v>
       </c>
       <c r="BA23" s="2">
         <f t="shared" si="65"/>
-        <v>607.83269194111813</v>
-      </c>
-    </row>
-    <row r="24" spans="2:56" x14ac:dyDescent="0.25">
+        <v>591.23230260616185</v>
+      </c>
+      <c r="BB23" s="2">
+        <f t="shared" si="65"/>
+        <v>608.72921368704431</v>
+      </c>
+      <c r="BC23" s="2">
+        <f t="shared" si="65"/>
+        <v>623.91423224642335</v>
+      </c>
+      <c r="BD23" s="2">
+        <f t="shared" si="65"/>
+        <v>637.02416955058368</v>
+      </c>
+      <c r="BE23" s="2">
+        <f t="shared" si="65"/>
+        <v>648.27209951904001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:60" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>32</v>
       </c>
@@ -4336,54 +4372,58 @@
       </c>
       <c r="Z24" s="1">
         <f t="shared" si="66"/>
-        <v>2.7201598212236999</v>
-      </c>
-      <c r="AQ24" s="1">
-        <f>+AQ23/AQ25</f>
-        <v>5.4509037004259087</v>
-      </c>
-      <c r="AR24" s="1">
-        <f t="shared" ref="AR24:BA24" si="67">+AR23/AR25</f>
-        <v>2.2539346792779829</v>
-      </c>
-      <c r="AS24" s="1">
-        <f t="shared" si="67"/>
-        <v>2.881587872633073</v>
-      </c>
-      <c r="AT24" s="1">
-        <f t="shared" si="67"/>
-        <v>3.4727370273709828</v>
-      </c>
+        <v>3.2633524546824026</v>
+      </c>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
       <c r="AU24" s="1">
-        <f t="shared" si="67"/>
-        <v>4.0310833737113922</v>
+        <f>+AU23/AU25</f>
+        <v>5.8524598336928655</v>
       </c>
       <c r="AV24" s="1">
-        <f t="shared" si="67"/>
-        <v>4.5599575105884345</v>
+        <f t="shared" ref="AV24:BE24" si="67">+AV23/AV25</f>
+        <v>7.9826668141674491</v>
       </c>
       <c r="AW24" s="1">
         <f t="shared" si="67"/>
-        <v>5.0623564738618851</v>
+        <v>3.2856029500156723</v>
       </c>
       <c r="AX24" s="1">
         <f t="shared" si="67"/>
-        <v>5.2275379325108444</v>
+        <v>3.8727119539797545</v>
       </c>
       <c r="AY24" s="1">
         <f t="shared" si="67"/>
-        <v>5.3713677092254271</v>
+        <v>4.4270585510540785</v>
       </c>
       <c r="AZ24" s="1">
         <f t="shared" si="67"/>
-        <v>5.4960293075597688</v>
+        <v>4.9519729361576923</v>
       </c>
       <c r="BA24" s="1">
         <f t="shared" si="67"/>
-        <v>5.6034873973589807</v>
-      </c>
-    </row>
-    <row r="25" spans="2:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>5.4504517451754504</v>
+      </c>
+      <c r="BB24" s="1">
+        <f t="shared" si="67"/>
+        <v>5.6117522511112732</v>
+      </c>
+      <c r="BC24" s="1">
+        <f t="shared" si="67"/>
+        <v>5.7517398846398526</v>
+      </c>
+      <c r="BD24" s="1">
+        <f t="shared" si="67"/>
+        <v>5.8725977612200495</v>
+      </c>
+      <c r="BE24" s="1">
+        <f t="shared" si="67"/>
+        <v>5.9762901664826593</v>
+      </c>
+    </row>
+    <row r="25" spans="2:60" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>1</v>
       </c>
@@ -4442,36 +4482,20 @@
         <f>+Y25</f>
         <v>100.23699999999999</v>
       </c>
-      <c r="AO25" s="2">
+      <c r="AS25" s="2">
         <f>R25</f>
         <v>105.59399999999999</v>
       </c>
-      <c r="AP25" s="2">
+      <c r="AT25" s="2">
         <f>+V25</f>
         <v>108.474</v>
       </c>
-      <c r="AQ25" s="2">
-        <f>+AP25</f>
+      <c r="AU25" s="2">
+        <f>+AT25</f>
         <v>108.474</v>
       </c>
-      <c r="AR25" s="2">
-        <f t="shared" ref="AR25:BA25" si="68">+AQ25</f>
-        <v>108.474</v>
-      </c>
-      <c r="AS25" s="2">
-        <f t="shared" si="68"/>
-        <v>108.474</v>
-      </c>
-      <c r="AT25" s="2">
-        <f t="shared" si="68"/>
-        <v>108.474</v>
-      </c>
-      <c r="AU25" s="2">
-        <f t="shared" si="68"/>
-        <v>108.474</v>
-      </c>
       <c r="AV25" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" ref="AV25:BE25" si="68">+AU25</f>
         <v>108.474</v>
       </c>
       <c r="AW25" s="2">
@@ -4494,16 +4518,32 @@
         <f t="shared" si="68"/>
         <v>108.474</v>
       </c>
-    </row>
-    <row r="26" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="BC26" t="s">
+      <c r="BB25" s="2">
+        <f t="shared" si="68"/>
+        <v>108.474</v>
+      </c>
+      <c r="BC25" s="2">
+        <f t="shared" si="68"/>
+        <v>108.474</v>
+      </c>
+      <c r="BD25" s="2">
+        <f t="shared" si="68"/>
+        <v>108.474</v>
+      </c>
+      <c r="BE25" s="2">
+        <f t="shared" si="68"/>
+        <v>108.474</v>
+      </c>
+    </row>
+    <row r="26" spans="2:60" x14ac:dyDescent="0.25">
+      <c r="BG26" t="s">
         <v>251</v>
       </c>
-      <c r="BD26" s="22">
+      <c r="BH26" s="22">
         <v>0.09</v>
       </c>
     </row>
-    <row r="27" spans="2:56" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:60" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>252</v>
       </c>
@@ -4525,11 +4565,15 @@
       </c>
       <c r="Z27" s="22">
         <f>+Z13/V13-1</f>
-        <v>-0.4950102892376852</v>
-      </c>
-      <c r="BD27" s="22"/>
-    </row>
-    <row r="28" spans="2:56" x14ac:dyDescent="0.25">
+        <v>-0.39416816638950269</v>
+      </c>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="22"/>
+      <c r="BH27" s="22"/>
+    </row>
+    <row r="28" spans="2:60" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>173</v>
       </c>
@@ -4569,37 +4613,41 @@
         <f>+Z15/Z13</f>
         <v>0.82</v>
       </c>
-      <c r="AO28" s="22">
-        <f t="shared" ref="AO28" si="71">+AO15/AO13</f>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="22"/>
+      <c r="AC28" s="22"/>
+      <c r="AD28" s="22"/>
+      <c r="AS28" s="22">
+        <f t="shared" ref="AS28" si="71">+AS15/AS13</f>
         <v>0.86868184851459884</v>
       </c>
-      <c r="AP28" s="22">
-        <f>+AP15/AP13</f>
+      <c r="AT28" s="22">
+        <f>+AT15/AT13</f>
         <v>0.821536191746009</v>
       </c>
-      <c r="BC28" t="s">
+      <c r="BG28" t="s">
         <v>250</v>
       </c>
-      <c r="BD28" s="2">
-        <f>NPV(BD26,AR23:BA23)+Main!L5-Main!L6</f>
-        <v>2518.8232204119381</v>
-      </c>
-    </row>
-    <row r="29" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="AP29" s="22">
-        <f>+AP13/AO13-1</f>
+      <c r="BH28" s="2">
+        <f>NPV(BH26,AV23:BE23)+Main!L5-Main!L6</f>
+        <v>3321.8851295339864</v>
+      </c>
+    </row>
+    <row r="29" spans="2:60" x14ac:dyDescent="0.25">
+      <c r="AT29" s="22">
+        <f>+AT13/AS13-1</f>
         <v>0.56176913482333446</v>
       </c>
-      <c r="AQ29" s="22">
-        <f>+AQ13/AP13-1</f>
-        <v>5.755489834633698E-3</v>
-      </c>
-      <c r="BD29" s="1">
-        <f>+BD28/Main!L3</f>
-        <v>25.967249694968434</v>
-      </c>
-    </row>
-    <row r="31" spans="2:56" x14ac:dyDescent="0.25">
+      <c r="AU29" s="22">
+        <f>+AU13/AT13-1</f>
+        <v>4.2891290536187343E-2</v>
+      </c>
+      <c r="BH29" s="1">
+        <f>+BH28/Main!L3</f>
+        <v>34.246238448803986</v>
+      </c>
+    </row>
+    <row r="31" spans="2:60" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>157</v>
       </c>
@@ -4616,7 +4664,7 @@
         <v>-183.15300000000002</v>
       </c>
     </row>
-    <row r="32" spans="2:56" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:60" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
         <v>3</v>
       </c>
